--- a/stories/arbres/ATOM-SAN.HYG.003-06.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Armand est dans la cuisine. Maman coupe une pomme. Le nez d'Armand chatouille. Atchoum. Tout doux. Maman tend un mouchoir. Armand prend un mouchoir. Il se mouche. Le nez est plus libre. Armand va jeter le mouchoir. Il le met dans la poubelle. Maman dit : mouchoir, puis poubelle. Armand va au lavabo. Il se lave les mains. Il revient près de maman. Maman sourit. Armand croque la pomme. Le nez est calme. Maman dit encore : mouchoir, puis poubelle. Armand hoche la tête.</t>
+          <t>Armand est dans la cuisine. Maman coupe une pomme. Le nez d'Armand chatouille. Atchoum. Tout doux. Maman tend un mouchoir. Armand prend un mouchoir. Il se mouche. Le nez est plus libre. Armand va jeter le mouchoir. Il le met dans la poubelle. Mouchoir, puis poubelle. Armand va au lavabo. Il se lave les mains. Il revient près de maman. Maman sourit. Armand croque la pomme. Le nez est calme. Maman dit encore : mouchoir, puis poubelle. Armand hoche la tête.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Armand est dans la cuisine. Maman coupe une pomme. Le nez d'Armand chatouille. Atchoum. Tout doux. Maman tend un mouchoir. Armand prend un mouchoir. Il se mouche. Le nez est plus libre. Armand va jeter le mouchoir. Il le met dans la poubelle.
+maman|Mouchoir, puis poubelle.
+narrateur|Armand va au lavabo. Il se lave les mains. Il revient près de maman. Maman sourit. Armand croque la pomme. Le nez est calme. Maman dit encore : mouchoir, puis poubelle. Armand hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le nez d'Armand chatouille. Que prend-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Armand a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Armand s'assoit près de maman. Son nez est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-06.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Armand va au lavabo. Il se lave les mains. Il revient près de maman. Maman sourit. Armand croque la pomme. Le nez est calme. Maman dit encore : mouchoir, puis poubelle. Armand hoche la tête.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Le nez d'Armand chatouille. Que prend-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Armand a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Armand s'assoit près de maman. Son nez est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.003-06.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le mouchoir d'Armand</t>
+          <t>La pomme d'Amir</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.HYG.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La bouilloire chante. Amir veut la pomme. Son nez chatouille. Maman tend un mouchoir. Il se mouche, jette, puis croque.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Armand est dans la cuisine. Maman coupe une pomme. Le nez d'Armand chatouille. Atchoum. Tout doux. Maman tend un mouchoir. Armand prend un mouchoir. Il se mouche. Le nez est plus libre. Armand va jeter le mouchoir. Il le met dans la poubelle. Mouchoir, puis poubelle. Armand va au lavabo. Il se lave les mains. Il revient près de maman. Maman sourit. Armand croque la pomme. Le nez est calme. Maman dit encore : mouchoir, puis poubelle. Armand hoche la tête.</t>
+          <t>La bouilloire chante. Une petite chanson. La vitre est chaude. Une goutte glisse. La pomme rouge brille. Elle est sur la planche. Une goutte de jus perle. Le frigo fait un ronron. Ça sent le fruit. Maman coupe tout doux. En ce moment, Amir lève le nez. Ça chatouille. Atchoum. Tout doux. Maman. Mon nez. Viens, Amir. J'ai un mouchoir. Maman tend le mouchoir. Il est blanc. Il est doux. Amir le prend. Il se mouche. Le nez est plus libre. Bravo, Amir. Tu as pris le mouchoir. On va à la poubelle ? Oui, maman. La poubelle est sous l'évier. Amir ouvre. Il jette le mouchoir. Toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. C'est du bon travail. Amir va au lavabo. L'eau est tiède. Il se lave les mains. Il essuie. Il revient. La pomme attend. Tu veux un morceau ? Oui. Amir croque. C'est sucré. Le nez est calme. Maman dit encore. Mouchoir, puis poubelle. Amir hoche la tête.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1329,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Armand est dans la cuisine. Maman coupe une pomme. Le nez d'Armand chatouille. Atchoum. Tout doux. Maman tend un mouchoir. Armand prend un mouchoir. Il se mouche. Le nez est plus libre. Armand va jeter le mouchoir. Il le met dans la poubelle.
+          <t>narrateur|La bouilloire chante.
+narrateur|Une petite chanson.
+narrateur|La vitre est chaude.
+narrateur|Une goutte glisse.
+narrateur|La pomme rouge brille.
+narrateur|Elle est sur la planche.
+narrateur|Une goutte de jus perle.
+narrateur|Le frigo fait un ronron.
+narrateur|Ça sent le fruit.
+narrateur|Maman coupe tout doux.
+narrateur|En ce moment, Amir lève le nez.
+narrateur|Ça chatouille.
+narrateur|Atchoum.
+narrateur|Tout doux.
+enfant-m|Maman.
+enfant-m|Mon nez.
+maman|Viens, Amir.
+maman|J'ai un mouchoir.
+narrateur|Maman tend le mouchoir.
+narrateur|Il est blanc.
+narrateur|Il est doux.
+narrateur|Amir le prend.
+narrateur|Il se mouche.
+narrateur|Le nez est plus libre.
+maman|Bravo, Amir.
+maman|Tu as pris le mouchoir.
+maman|On va à la poubelle ?
+enfant-m|Oui, maman.
+narrateur|La poubelle est sous l'évier.
+narrateur|Amir ouvre.
+narrateur|Il jette le mouchoir.
+narrateur|Toc.
 maman|Mouchoir, puis poubelle.
-narrateur|Armand va au lavabo. Il se lave les mains. Il revient près de maman. Maman sourit. Armand croque la pomme. Le nez est calme. Maman dit encore : mouchoir, puis poubelle. Armand hoche la tête.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|Mouchoir, puis poubelle.
+maman|C'est du bon travail.
+narrateur|Amir va au lavabo.
+narrateur|L'eau est tiède.
+narrateur|Il se lave les mains.
+narrateur|Il essuie.
+narrateur|Il revient.
+narrateur|La pomme attend.
+maman|Tu veux un morceau ?
+enfant-m|Oui.
+narrateur|Amir croque.
+enfant-m|C'est sucré.
+narrateur|Le nez est calme.
+narrateur|Maman dit encore.
+maman|Mouchoir, puis poubelle.
+narrateur|Amir hoche la tête.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>bouilloire,poubelle</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le nez d'Armand chatouille. Que prend-il ?</t>
+          <t>Le nez d'Amir chatouille. Que prend-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le nez d'Armand chatouille. Que prend-il ?</t>
+          <t>narrateur|Le nez d'Amir chatouille.
+narrateur|Que prend-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Armand a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
+          <t>Amir a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir. Bravo. C'est du bon travail. Mouchoir, puis poubelle. Oui, maman. La pomme est encore là. Un morceau rouge brille. Tu as fini ton morceau ? Presque. Amir croque encore. C'est sucré. Le frigo ronronne. La cuisine est calme.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1738,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Armand a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
+          <t>narrateur|Amir a pris un mouchoir.
+narrateur|Il s'est mouché.
+narrateur|Il a jeté le mouchoir.
+maman|Bravo.
+maman|C'est du bon travail.
+maman|Mouchoir, puis poubelle.
+enfant-m|Oui, maman.
+narrateur|La pomme est encore là.
+narrateur|Un morceau rouge brille.
+maman|Tu as fini ton morceau ?
+enfant-m|Presque.
+narrateur|Amir croque encore.
+enfant-m|C'est sucré.
+narrateur|Le frigo ronronne.
+narrateur|La cuisine est calme.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Armand s'assoit près de maman. Son nez est calme.</t>
+          <t>Amir s'assoit près de maman. La chaise est un peu froide. Son nez est calme. Maman verse un peu d'eau. L'eau fait un petit bruit. Tu veux de l'eau ? Oui. Merci, maman. Amir boit une gorgée. La goutte sur la vitre est partie. On reste un peu ? Oui. La bouilloire s'est tue. La pomme sent encore bon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,7 +1916,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Armand s'assoit près de maman. Son nez est calme.</t>
+          <t>narrateur|Amir s'assoit près de maman.
+narrateur|La chaise est un peu froide.
+narrateur|Son nez est calme.
+narrateur|Maman verse un peu d'eau.
+narrateur|L'eau fait un petit bruit.
+maman|Tu veux de l'eau ?
+enfant-m|Oui.
+enfant-m|Merci, maman.
+narrateur|Amir boit une gorgée.
+narrateur|La goutte sur la vitre est partie.
+maman|On reste un peu ?
+enfant-m|Oui.
+narrateur|La bouilloire s'est tue.
+narrateur|La pomme sent encore bon.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1862,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. Tu as fait du bon travail. La pomme était sucrée. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,7 +2097,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai pris un mouchoir.
+enfant-m|Puis la poubelle.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|La pomme était sucrée.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2024,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-06.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-06.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La bouilloire chante. Une petite chanson. La vitre est chaude. Une goutte glisse. La pomme rouge brille. Elle est sur la planche. Une goutte de jus perle. Le frigo fait un ronron. Ça sent le fruit. Maman coupe tout doux. En ce moment, Amir lève le nez. Ça chatouille. Atchoum. Tout doux. Maman. Mon nez. Viens, Amir. J'ai un mouchoir. Maman tend le mouchoir. Il est blanc. Il est doux. Amir le prend. Il se mouche. Le nez est plus libre. Bravo, Amir. Tu as pris le mouchoir. On va à la poubelle ? Oui, maman. La poubelle est sous l'évier. Amir ouvre. Il jette le mouchoir. Toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. C'est du bon travail. Amir va au lavabo. L'eau est tiède. Il se lave les mains. Il essuie. Il revient. La pomme attend. Tu veux un morceau ? Oui. Amir croque. C'est sucré. Le nez est calme. Maman dit encore. Mouchoir, puis poubelle. Amir hoche la tête.</t>
+          <t>La bouilloire chante. Une petite chanson. La vitre est chaude. Une goutte glisse. Dehors, un chat passe. Il marche sur le muret. La pomme rouge brille. Elle est sur la planche. Le bois de la planche est rayé. Une goutte de jus perle. Une épluchure fait une spirale. Elle est rouge et blanche. Le frigo fait un ronron. Ça sent le fruit. Maman coupe tout doux. Maman, c'est une vis ? C'est l'épluchure. Tu as bien regardé. En ce moment, Amir lève le nez. Ça chatouille. Atchoum. Tout doux. Maman. Mon nez. Viens, Amir. J'ai un mouchoir. Maman tend le mouchoir. Il est blanc. Il est doux. Amir le prend. Il se mouche. Le nez est plus libre. Bravo, Amir. Tu as pris le mouchoir. On va à la poubelle ? Oui, maman. La poubelle est sous l'évier. Amir ouvre. Il jette le mouchoir. Toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. Tu as fini de jeter le mouchoir ? Oui. Amir va au lavabo. L'eau est tiède. Il se lave les mains. Le savon sent le citron. Il essuie. Il revient. Il s'assoit. La chaise fait un petit bruit. La pomme attend. Tu veux un morceau ? Oui. Amir croque. C'est sucré. Le nez est calme. Mouchoir, puis poubelle. Amir hoche la tête.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Armand est dans la cuisine. Maman coupe une pomme. Le nez d'Armand chatouille. Atchoum. Tout doux. Maman tend un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Armand prend un mouchoir. Il se mouche. Le nez est plus libre. Armand va jeter le mouchoir. Il le met dans la poubelle. Maman dit : mouchoir, puis poubelle. Armand va au lavabo. Il se lave les mains. Il revient près de maman. Maman sourit. Armand croque la pomme. Le nez est calme. Maman dit encore : mouchoir, puis poubelle. Armand hoche la tête.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La bouilloire chante. Une petite chanson. La vitre est chaude. Une goutte glisse. Dehors, un chat passe. Il marche sur le muret. La pomme rouge brille. Elle est sur la planche. Le bois de la planche est rayé. Une goutte de jus perle. Une épluchure fait une spirale. Elle est rouge et blanche. Le frigo fait un ronron. Ça sent le fruit. Maman coupe tout doux. Maman, c'est une vis ? C'est l'épluchure. Tu as bien regardé. En ce moment, Amir lève le nez. Ça chatouille. Atchoum. Tout doux. Maman. Mon nez. Viens, Amir. J'ai un mouchoir. Maman tend le mouchoir. Il est blanc. Il est doux. Amir le prend. Il se mouche. Le nez est plus libre. Bravo, Amir. Tu as pris le mouchoir. On va à la poubelle ? Oui, maman. La poubelle est sous l'évier. Amir ouvre. Il jette le mouchoir. Toc. Mouchoir, puis poubelle. Mouchoir, puis poubelle. Tu as fini de jeter le mouchoir ? Oui. Amir va au lavabo. L'eau est tiède. Il se lave les mains. Le savon sent le citron. Il essuie. Il revient. Il s'assoit. La chaise fait un petit bruit. La pomme attend. Tu veux un morceau ? Oui. Amir croque. C'est sucré. Le nez est calme. Mouchoir, puis poubelle. Amir hoche la tête.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1333,12 +1333,20 @@
 narrateur|Une petite chanson.
 narrateur|La vitre est chaude.
 narrateur|Une goutte glisse.
+narrateur|Dehors, un chat passe.
+narrateur|Il marche sur le muret.
 narrateur|La pomme rouge brille.
 narrateur|Elle est sur la planche.
+narrateur|Le bois de la planche est rayé.
 narrateur|Une goutte de jus perle.
+narrateur|Une épluchure fait une spirale.
+narrateur|Elle est rouge et blanche.
 narrateur|Le frigo fait un ronron.
 narrateur|Ça sent le fruit.
 narrateur|Maman coupe tout doux.
+enfant-m|Maman, c'est une vis ?
+maman|C'est l'épluchure.
+maman|Tu as bien regardé.
 narrateur|En ce moment, Amir lève le nez.
 narrateur|Ça chatouille.
 narrateur|Atchoum.
@@ -1363,19 +1371,22 @@
 narrateur|Toc.
 maman|Mouchoir, puis poubelle.
 enfant-m|Mouchoir, puis poubelle.
-maman|C'est du bon travail.
+maman|Tu as fini de jeter le mouchoir ?
+enfant-m|Oui.
 narrateur|Amir va au lavabo.
 narrateur|L'eau est tiède.
 narrateur|Il se lave les mains.
+narrateur|Le savon sent le citron.
 narrateur|Il essuie.
 narrateur|Il revient.
+narrateur|Il s'assoit.
+narrateur|La chaise fait un petit bruit.
 narrateur|La pomme attend.
 maman|Tu veux un morceau ?
 enfant-m|Oui.
 narrateur|Amir croque.
 enfant-m|C'est sucré.
 narrateur|Le nez est calme.
-narrateur|Maman dit encore.
 maman|Mouchoir, puis poubelle.
 narrateur|Amir hoche la tête.</t>
         </is>
@@ -1414,7 +1425,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le nez d'Armand chatouille. Que prend-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le nez d'Amir chatouille. Que prend-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1580,6 @@
 narrateur|Que prend-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1604,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir. Bravo. C'est du bon travail. Mouchoir, puis poubelle. Oui, maman. La pomme est encore là. Un morceau rouge brille. Tu as fini ton morceau ? Presque. Amir croque encore. C'est sucré. Le frigo ronronne. La cuisine est calme.</t>
+          <t>Amir a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir. Bravo. Mouchoir, puis poubelle. Oui, maman. La pomme est encore là. Un morceau rouge brille. Tu as fini ton morceau ? Presque. Amir croque encore. C'est sucré. Le frigo ronronne. La cuisine est calme.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Armand a pris un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Il s'est mouché. Il a jeté le mouchoir à la poubelle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir. Bravo. Mouchoir, puis poubelle. Oui, maman. La pomme est encore là. Un morceau rouge brille. Tu as fini ton morceau ? Presque. Amir croque encore. C'est sucré. Le frigo ronronne. La cuisine est calme.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1742,7 +1752,6 @@
 narrateur|Il s'est mouché.
 narrateur|Il a jeté le mouchoir.
 maman|Bravo.
-maman|C'est du bon travail.
 maman|Mouchoir, puis poubelle.
 enfant-m|Oui, maman.
 narrateur|La pomme est encore là.
@@ -1755,7 +1764,6 @@
 narrateur|La cuisine est calme.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1780,12 +1788,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amir s'assoit près de maman. La chaise est un peu froide. Son nez est calme. Maman verse un peu d'eau. L'eau fait un petit bruit. Tu veux de l'eau ? Oui. Merci, maman. Amir boit une gorgée. La goutte sur la vitre est partie. On reste un peu ? Oui. La bouilloire s'est tue. La pomme sent encore bon.</t>
+          <t>Amir s'assoit près de maman. La chaise est un peu froide. Son nez est calme. Maman verse un peu d'eau. L'eau fait un petit bruit. Tu veux de l'eau ? Oui. Merci, maman. Amir boit une gorgée. La goutte sur la vitre est partie. Le chat n'est plus sur le muret. Tu as vu le chat, tout à l'heure ? Oui. Sur le muret. On reste un peu ? Oui. La bouilloire s'est tue. La pomme sent encore bon. L'épluchure fait encore une spirale. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Armand s'assoit près de maman. Son nez est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir s'assoit près de maman. La chaise est un peu froide. Son nez est calme. Maman verse un peu d'eau. L'eau fait un petit bruit. Tu veux de l'eau ? Oui. Merci, maman. Amir boit une gorgée. La goutte sur la vitre est partie. Le chat n'est plus sur le muret. Tu as vu le chat, tout à l'heure ? Oui. Sur le muret. On reste un peu ? Oui. La bouilloire s'est tue. La pomme sent encore bon. L'épluchure fait encore une spirale. Bravo, Amir.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1926,13 +1934,18 @@
 enfant-m|Merci, maman.
 narrateur|Amir boit une gorgée.
 narrateur|La goutte sur la vitre est partie.
+narrateur|Le chat n'est plus sur le muret.
+maman|Tu as vu le chat, tout à l'heure ?
+enfant-m|Oui.
+enfant-m|Sur le muret.
 maman|On reste un peu ?
 enfant-m|Oui.
 narrateur|La bouilloire s'est tue.
-narrateur|La pomme sent encore bon.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|La pomme sent encore bon.
+narrateur|L'épluchure fait encore une spirale.
+maman|Bravo, Amir.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. Tu as fait du bon travail. La pomme était sucrée. L'histoire est finie.</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. La pomme était sucrée.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. La pomme était sucrée.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,12 +2113,9 @@
           <t>enfant-m|J'ai pris un mouchoir.
 enfant-m|Puis la poubelle.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-maman|La pomme était sucrée.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|La pomme était sucrée.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2124,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2179,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-06.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-06.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Armand, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
